--- a/港岛-跑马地-339 Tai Hang Road/339 Tai Hang Road_销控明细表.xlsx
+++ b/港岛-跑马地-339 Tai Hang Road/339 Tai Hang Road_销控明细表.xlsx
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>49514400</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>32878</v>
+        <v>32856</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>50652880</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>33634</v>
+        <v>33612</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1422,9 +1422,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>- | 1506呎 (3房)
+          <t>- | 1507呎 (3房)
 $4951万
-$32,878/呎
+$32,856/呎
 (15年-02月-02日)</t>
         </is>
       </c>
@@ -1437,9 +1437,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>- | 1506呎 (3房)
+          <t>- | 1507呎 (3房)
 $5065万
-$33,634/呎
+$33,612/呎
 (15年-03月-29日)</t>
         </is>
       </c>
